--- a/data/Administracion_de_viviendas_publicas/datos_vivienda.xlsx
+++ b/data/Administracion_de_viviendas_publicas/datos_vivienda.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Administracion_de_viviendas_publicas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B47C1E-6D21-48AF-A626-F80B89258D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D27232-8002-46D8-BDBF-16430A4EB2F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" tabRatio="847" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="municipios_soli" sheetId="1" r:id="rId1"/>
@@ -903,14 +903,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>81</v>
       </c>
@@ -941,8 +941,11 @@
       <c r="J1" s="1">
         <v>2024</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -973,8 +976,11 @@
       <c r="J2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1005,8 +1011,11 @@
       <c r="J3">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1037,8 +1046,11 @@
       <c r="J4">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1069,8 +1081,11 @@
       <c r="J5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1101,8 +1116,11 @@
       <c r="J6">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1133,8 +1151,11 @@
       <c r="J7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1165,8 +1186,11 @@
       <c r="J8">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1197,8 +1221,11 @@
       <c r="J9">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1229,8 +1256,11 @@
       <c r="J10">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1261,8 +1291,11 @@
       <c r="J11">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>64</v>
       </c>
@@ -1293,8 +1326,11 @@
       <c r="J12">
         <v>34</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K12">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1325,8 +1361,11 @@
       <c r="J13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1357,8 +1396,11 @@
       <c r="J14">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1389,8 +1431,11 @@
       <c r="J15">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>65</v>
       </c>
@@ -1421,8 +1466,11 @@
       <c r="J16">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1453,8 +1501,11 @@
       <c r="J17">
         <v>32</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K17">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>66</v>
       </c>
@@ -1485,8 +1536,11 @@
       <c r="J18">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -1517,8 +1571,11 @@
       <c r="J19">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1549,8 +1606,11 @@
       <c r="J20">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -1581,8 +1641,11 @@
       <c r="J21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -1613,8 +1676,11 @@
       <c r="J22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K22">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -1645,8 +1711,11 @@
       <c r="J23">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>67</v>
       </c>
@@ -1677,8 +1746,11 @@
       <c r="J24">
         <v>9</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -1709,8 +1781,11 @@
       <c r="J25">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>79</v>
       </c>
@@ -1741,8 +1816,11 @@
       <c r="J26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -1773,8 +1851,11 @@
       <c r="J27">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>22</v>
       </c>
@@ -1805,8 +1886,11 @@
       <c r="J28">
         <v>9</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>23</v>
       </c>
@@ -1837,8 +1921,11 @@
       <c r="J29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -1869,8 +1956,11 @@
       <c r="J30">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -1901,8 +1991,11 @@
       <c r="J31">
         <v>18</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K31">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -1933,8 +2026,11 @@
       <c r="J32">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>26</v>
       </c>
@@ -1965,8 +2061,11 @@
       <c r="J33">
         <v>10</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>27</v>
       </c>
@@ -1997,8 +2096,11 @@
       <c r="J34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>28</v>
       </c>
@@ -2029,8 +2131,11 @@
       <c r="J35">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>29</v>
       </c>
@@ -2061,8 +2166,11 @@
       <c r="J36">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>30</v>
       </c>
@@ -2093,8 +2201,11 @@
       <c r="J37">
         <v>9</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K37">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>31</v>
       </c>
@@ -2125,8 +2236,11 @@
       <c r="J38">
         <v>2</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>32</v>
       </c>
@@ -2157,8 +2271,11 @@
       <c r="J39">
         <v>3</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>69</v>
       </c>
@@ -2189,8 +2306,11 @@
       <c r="J40">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>33</v>
       </c>
@@ -2221,8 +2341,11 @@
       <c r="J41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>34</v>
       </c>
@@ -2253,8 +2376,11 @@
       <c r="J42">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>35</v>
       </c>
@@ -2285,8 +2411,11 @@
       <c r="J43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -2317,8 +2446,11 @@
       <c r="J44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -2349,8 +2481,11 @@
       <c r="J45">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>70</v>
       </c>
@@ -2381,8 +2516,11 @@
       <c r="J46">
         <v>2</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>38</v>
       </c>
@@ -2413,8 +2551,11 @@
       <c r="J47">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>71</v>
       </c>
@@ -2445,8 +2586,11 @@
       <c r="J48">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K48">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>39</v>
       </c>
@@ -2477,8 +2621,11 @@
       <c r="J49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>40</v>
       </c>
@@ -2509,8 +2656,11 @@
       <c r="J50">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>78</v>
       </c>
@@ -2541,8 +2691,11 @@
       <c r="J51">
         <v>11</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K51">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>41</v>
       </c>
@@ -2573,8 +2726,11 @@
       <c r="J52">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>42</v>
       </c>
@@ -2605,8 +2761,11 @@
       <c r="J53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2796,11 @@
       <c r="J54">
         <v>2</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>44</v>
       </c>
@@ -2669,8 +2831,11 @@
       <c r="J55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>45</v>
       </c>
@@ -2701,8 +2866,11 @@
       <c r="J56">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K56">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>46</v>
       </c>
@@ -2733,8 +2901,11 @@
       <c r="J57">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>72</v>
       </c>
@@ -2765,8 +2936,11 @@
       <c r="J58">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>47</v>
       </c>
@@ -2797,8 +2971,11 @@
       <c r="J59">
         <v>36</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K59">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>48</v>
       </c>
@@ -2829,8 +3006,11 @@
       <c r="J60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>73</v>
       </c>
@@ -2861,8 +3041,11 @@
       <c r="J61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>74</v>
       </c>
@@ -2893,8 +3076,11 @@
       <c r="J62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K62">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>49</v>
       </c>
@@ -2925,8 +3111,11 @@
       <c r="J63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>50</v>
       </c>
@@ -2957,8 +3146,11 @@
       <c r="J64">
         <v>6</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K64">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>75</v>
       </c>
@@ -2989,8 +3181,11 @@
       <c r="J65">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K65">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>51</v>
       </c>
@@ -3021,8 +3216,11 @@
       <c r="J66">
         <v>69</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K66">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>52</v>
       </c>
@@ -3053,8 +3251,11 @@
       <c r="J67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>76</v>
       </c>
@@ -3085,8 +3286,11 @@
       <c r="J68">
         <v>3</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K68">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>53</v>
       </c>
@@ -3117,8 +3321,11 @@
       <c r="J69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>54</v>
       </c>
@@ -3149,8 +3356,11 @@
       <c r="J70">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>55</v>
       </c>
@@ -3181,8 +3391,11 @@
       <c r="J71">
         <v>4</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>56</v>
       </c>
@@ -3213,8 +3426,11 @@
       <c r="J72">
         <v>9</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K72">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>57</v>
       </c>
@@ -3245,8 +3461,11 @@
       <c r="J73">
         <v>2</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>58</v>
       </c>
@@ -3277,8 +3496,11 @@
       <c r="J74">
         <v>5</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K74">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>59</v>
       </c>
@@ -3309,8 +3531,11 @@
       <c r="J75">
         <v>2</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>60</v>
       </c>
@@ -3341,8 +3566,11 @@
       <c r="J76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>61</v>
       </c>
@@ -3373,8 +3601,11 @@
       <c r="J77">
         <v>4</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>62</v>
       </c>
@@ -3405,8 +3636,11 @@
       <c r="J78">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>63</v>
       </c>
@@ -3436,6 +3670,9 @@
       </c>
       <c r="J79">
         <v>3</v>
+      </c>
+      <c r="K79">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3446,14 +3683,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>81</v>
       </c>
@@ -3484,8 +3721,11 @@
       <c r="J1" s="1">
         <v>2024</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -3516,8 +3756,11 @@
       <c r="J2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3548,8 +3791,11 @@
       <c r="J3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -3580,8 +3826,11 @@
       <c r="J4">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3612,8 +3861,11 @@
       <c r="J5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -3644,8 +3896,11 @@
       <c r="J6">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -3676,8 +3931,11 @@
       <c r="J7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -3708,8 +3966,11 @@
       <c r="J8">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -3740,8 +4001,11 @@
       <c r="J9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -3772,8 +4036,11 @@
       <c r="J10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -3804,8 +4071,11 @@
       <c r="J11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>64</v>
       </c>
@@ -3836,8 +4106,11 @@
       <c r="J12">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K12">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -3868,8 +4141,11 @@
       <c r="J13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -3900,8 +4176,11 @@
       <c r="J14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -3932,8 +4211,11 @@
       <c r="J15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>65</v>
       </c>
@@ -3964,8 +4246,11 @@
       <c r="J16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -3996,8 +4281,11 @@
       <c r="J17">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>66</v>
       </c>
@@ -4028,8 +4316,11 @@
       <c r="J18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -4060,8 +4351,11 @@
       <c r="J19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -4092,8 +4386,11 @@
       <c r="J20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -4124,8 +4421,11 @@
       <c r="J21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -4156,8 +4456,11 @@
       <c r="J22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -4188,8 +4491,11 @@
       <c r="J23">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>67</v>
       </c>
@@ -4220,8 +4526,11 @@
       <c r="J24">
         <v>2</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -4252,8 +4561,11 @@
       <c r="J25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>79</v>
       </c>
@@ -4284,8 +4596,11 @@
       <c r="J26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -4316,8 +4631,11 @@
       <c r="J27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>22</v>
       </c>
@@ -4348,8 +4666,11 @@
       <c r="J28">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>23</v>
       </c>
@@ -4380,8 +4701,11 @@
       <c r="J29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -4412,8 +4736,11 @@
       <c r="J30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -4444,8 +4771,11 @@
       <c r="J31">
         <v>10</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K31">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -4476,8 +4806,11 @@
       <c r="J32">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>26</v>
       </c>
@@ -4508,8 +4841,11 @@
       <c r="J33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>27</v>
       </c>
@@ -4540,8 +4876,11 @@
       <c r="J34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>28</v>
       </c>
@@ -4572,8 +4911,11 @@
       <c r="J35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>29</v>
       </c>
@@ -4604,8 +4946,11 @@
       <c r="J36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>30</v>
       </c>
@@ -4636,8 +4981,11 @@
       <c r="J37">
         <v>6</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K37">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>31</v>
       </c>
@@ -4668,8 +5016,11 @@
       <c r="J38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>32</v>
       </c>
@@ -4700,8 +5051,11 @@
       <c r="J39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>69</v>
       </c>
@@ -4732,8 +5086,11 @@
       <c r="J40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>33</v>
       </c>
@@ -4764,8 +5121,11 @@
       <c r="J41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>34</v>
       </c>
@@ -4796,8 +5156,11 @@
       <c r="J42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>35</v>
       </c>
@@ -4828,8 +5191,11 @@
       <c r="J43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -4860,8 +5226,11 @@
       <c r="J44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -4892,8 +5261,11 @@
       <c r="J45">
         <v>2</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>70</v>
       </c>
@@ -4924,8 +5296,11 @@
       <c r="J46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>38</v>
       </c>
@@ -4956,8 +5331,11 @@
       <c r="J47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>71</v>
       </c>
@@ -4988,8 +5366,11 @@
       <c r="J48">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K48">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>39</v>
       </c>
@@ -5020,8 +5401,11 @@
       <c r="J49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>40</v>
       </c>
@@ -5052,8 +5436,11 @@
       <c r="J50">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>78</v>
       </c>
@@ -5084,8 +5471,11 @@
       <c r="J51">
         <v>9</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K51">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>41</v>
       </c>
@@ -5116,8 +5506,11 @@
       <c r="J52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>42</v>
       </c>
@@ -5148,8 +5541,11 @@
       <c r="J53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>43</v>
       </c>
@@ -5180,8 +5576,11 @@
       <c r="J54">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>44</v>
       </c>
@@ -5212,8 +5611,11 @@
       <c r="J55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>45</v>
       </c>
@@ -5244,8 +5646,11 @@
       <c r="J56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>46</v>
       </c>
@@ -5276,8 +5681,11 @@
       <c r="J57">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>72</v>
       </c>
@@ -5308,8 +5716,11 @@
       <c r="J58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>47</v>
       </c>
@@ -5340,8 +5751,11 @@
       <c r="J59">
         <v>26</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K59">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>48</v>
       </c>
@@ -5372,8 +5786,11 @@
       <c r="J60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>73</v>
       </c>
@@ -5404,8 +5821,11 @@
       <c r="J61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>74</v>
       </c>
@@ -5436,8 +5856,11 @@
       <c r="J62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>49</v>
       </c>
@@ -5468,8 +5891,11 @@
       <c r="J63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>50</v>
       </c>
@@ -5500,8 +5926,11 @@
       <c r="J64">
         <v>2</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K64">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>75</v>
       </c>
@@ -5532,8 +5961,11 @@
       <c r="J65">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K65">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>51</v>
       </c>
@@ -5564,8 +5996,11 @@
       <c r="J66">
         <v>38</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>52</v>
       </c>
@@ -5596,8 +6031,11 @@
       <c r="J67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>76</v>
       </c>
@@ -5628,8 +6066,11 @@
       <c r="J68">
         <v>3</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K68">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>53</v>
       </c>
@@ -5660,8 +6101,11 @@
       <c r="J69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>54</v>
       </c>
@@ -5692,8 +6136,11 @@
       <c r="J70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>55</v>
       </c>
@@ -5724,8 +6171,11 @@
       <c r="J71">
         <v>3</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>56</v>
       </c>
@@ -5756,8 +6206,11 @@
       <c r="J72">
         <v>2</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K72">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>57</v>
       </c>
@@ -5788,8 +6241,11 @@
       <c r="J73">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>58</v>
       </c>
@@ -5820,8 +6276,11 @@
       <c r="J74">
         <v>2</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K74">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>59</v>
       </c>
@@ -5852,8 +6311,11 @@
       <c r="J75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>60</v>
       </c>
@@ -5884,8 +6346,11 @@
       <c r="J76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>61</v>
       </c>
@@ -5916,8 +6381,11 @@
       <c r="J77">
         <v>3</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>62</v>
       </c>
@@ -5948,8 +6416,11 @@
       <c r="J78">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>63</v>
       </c>
@@ -5979,6 +6450,9 @@
       </c>
       <c r="J79">
         <v>3</v>
+      </c>
+      <c r="K79">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5988,13 +6462,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
@@ -6022,8 +6496,11 @@
       <c r="I1" s="1">
         <v>2024</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -6051,8 +6528,11 @@
       <c r="I2">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6080,8 +6560,11 @@
       <c r="I3">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -6107,10 +6590,13 @@
         <v>58</v>
       </c>
       <c r="I4">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+      <c r="J4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -6138,8 +6624,11 @@
       <c r="I5">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -6167,8 +6656,11 @@
       <c r="I6">
         <v>65</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J6">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -6196,8 +6688,11 @@
       <c r="I7">
         <v>39</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J7">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -6225,8 +6720,11 @@
       <c r="I8">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>78</v>
       </c>
@@ -6254,8 +6752,11 @@
       <c r="I9">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -6281,10 +6782,13 @@
         <v>33</v>
       </c>
       <c r="I10">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+      <c r="J10">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -6311,6 +6815,9 @@
       </c>
       <c r="I11">
         <v>69</v>
+      </c>
+      <c r="J11">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -6323,13 +6830,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
@@ -6357,8 +6864,11 @@
       <c r="I1" s="1">
         <v>2024</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -6386,8 +6896,11 @@
       <c r="I2">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6415,8 +6928,11 @@
       <c r="I3">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -6444,8 +6960,11 @@
       <c r="I4">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -6473,8 +6992,11 @@
       <c r="I5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -6502,8 +7024,11 @@
       <c r="I6">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -6529,10 +7054,13 @@
         <v>4</v>
       </c>
       <c r="I7">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="J7">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -6560,8 +7088,11 @@
       <c r="I8">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>78</v>
       </c>
@@ -6589,8 +7120,11 @@
       <c r="I9">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -6616,10 +7150,13 @@
         <v>21</v>
       </c>
       <c r="I10">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+      <c r="J10">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -6646,6 +7183,9 @@
       </c>
       <c r="I11">
         <v>38</v>
+      </c>
+      <c r="J11">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/data/Administracion_de_viviendas_publicas/datos_vivienda.xlsx
+++ b/data/Administracion_de_viviendas_publicas/datos_vivienda.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Administracion_de_viviendas_publicas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D27232-8002-46D8-BDBF-16430A4EB2F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63A84D35-9E04-4D95-9B3A-E0AE45AA53F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" tabRatio="847" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" tabRatio="847" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="municipios_soli" sheetId="1" r:id="rId1"/>
@@ -903,14 +903,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>81</v>
       </c>
@@ -944,8 +944,11 @@
       <c r="K1" s="1">
         <v>2025</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -979,8 +982,11 @@
       <c r="K2">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1014,8 +1020,11 @@
       <c r="K3">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1049,8 +1058,11 @@
       <c r="K4">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1084,8 +1096,11 @@
       <c r="K5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1119,8 +1134,11 @@
       <c r="K6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1154,8 +1172,11 @@
       <c r="K7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1189,8 +1210,11 @@
       <c r="K8">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1224,8 +1248,11 @@
       <c r="K9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1259,8 +1286,11 @@
       <c r="K10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1294,8 +1324,11 @@
       <c r="K11">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>64</v>
       </c>
@@ -1329,8 +1362,11 @@
       <c r="K12">
         <v>26</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1364,8 +1400,11 @@
       <c r="K13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1399,8 +1438,11 @@
       <c r="K14">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1434,8 +1476,11 @@
       <c r="K15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>65</v>
       </c>
@@ -1469,8 +1514,11 @@
       <c r="K16">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1504,8 +1552,11 @@
       <c r="K17">
         <v>26</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L17">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>66</v>
       </c>
@@ -1539,8 +1590,11 @@
       <c r="K18">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -1574,8 +1628,11 @@
       <c r="K19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1609,8 +1666,11 @@
       <c r="K20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -1644,8 +1704,11 @@
       <c r="K21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -1679,8 +1742,11 @@
       <c r="K22">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -1714,8 +1780,11 @@
       <c r="K23">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>67</v>
       </c>
@@ -1749,8 +1818,11 @@
       <c r="K24">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -1784,8 +1856,11 @@
       <c r="K25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>79</v>
       </c>
@@ -1819,8 +1894,11 @@
       <c r="K26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -1854,8 +1932,11 @@
       <c r="K27">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>22</v>
       </c>
@@ -1889,8 +1970,11 @@
       <c r="K28">
         <v>7</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>23</v>
       </c>
@@ -1924,8 +2008,11 @@
       <c r="K29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -1959,8 +2046,11 @@
       <c r="K30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -1994,8 +2084,11 @@
       <c r="K31">
         <v>14</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -2029,8 +2122,11 @@
       <c r="K32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>26</v>
       </c>
@@ -2064,8 +2160,11 @@
       <c r="K33">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>27</v>
       </c>
@@ -2099,8 +2198,11 @@
       <c r="K34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>28</v>
       </c>
@@ -2134,8 +2236,11 @@
       <c r="K35">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>29</v>
       </c>
@@ -2169,8 +2274,11 @@
       <c r="K36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>30</v>
       </c>
@@ -2204,8 +2312,11 @@
       <c r="K37">
         <v>12</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>31</v>
       </c>
@@ -2239,8 +2350,11 @@
       <c r="K38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>32</v>
       </c>
@@ -2274,8 +2388,11 @@
       <c r="K39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>69</v>
       </c>
@@ -2309,8 +2426,11 @@
       <c r="K40">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>33</v>
       </c>
@@ -2344,8 +2464,11 @@
       <c r="K41">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>34</v>
       </c>
@@ -2379,8 +2502,11 @@
       <c r="K42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>35</v>
       </c>
@@ -2414,8 +2540,11 @@
       <c r="K43">
         <v>2</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -2449,8 +2578,11 @@
       <c r="K44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -2484,8 +2616,11 @@
       <c r="K45">
         <v>2</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>70</v>
       </c>
@@ -2519,8 +2654,11 @@
       <c r="K46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>38</v>
       </c>
@@ -2554,8 +2692,11 @@
       <c r="K47">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>71</v>
       </c>
@@ -2589,8 +2730,11 @@
       <c r="K48">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>39</v>
       </c>
@@ -2624,8 +2768,11 @@
       <c r="K49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>40</v>
       </c>
@@ -2659,8 +2806,11 @@
       <c r="K50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>78</v>
       </c>
@@ -2694,8 +2844,11 @@
       <c r="K51">
         <v>10</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L51">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>41</v>
       </c>
@@ -2729,8 +2882,11 @@
       <c r="K52">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>42</v>
       </c>
@@ -2764,8 +2920,11 @@
       <c r="K53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>43</v>
       </c>
@@ -2799,8 +2958,11 @@
       <c r="K54">
         <v>2</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>44</v>
       </c>
@@ -2834,8 +2996,11 @@
       <c r="K55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>45</v>
       </c>
@@ -2869,8 +3034,11 @@
       <c r="K56">
         <v>3</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>46</v>
       </c>
@@ -2904,8 +3072,11 @@
       <c r="K57">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>72</v>
       </c>
@@ -2939,8 +3110,11 @@
       <c r="K58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>47</v>
       </c>
@@ -2974,8 +3148,11 @@
       <c r="K59">
         <v>27</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L59">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>48</v>
       </c>
@@ -3009,8 +3186,11 @@
       <c r="K60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>73</v>
       </c>
@@ -3044,8 +3224,11 @@
       <c r="K61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>74</v>
       </c>
@@ -3079,8 +3262,11 @@
       <c r="K62">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>49</v>
       </c>
@@ -3114,8 +3300,11 @@
       <c r="K63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>50</v>
       </c>
@@ -3149,8 +3338,11 @@
       <c r="K64">
         <v>6</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L64">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>75</v>
       </c>
@@ -3184,8 +3376,11 @@
       <c r="K65">
         <v>3</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L65">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>51</v>
       </c>
@@ -3219,8 +3414,11 @@
       <c r="K66">
         <v>91</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L66">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>52</v>
       </c>
@@ -3254,8 +3452,11 @@
       <c r="K67">
         <v>2</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>76</v>
       </c>
@@ -3289,8 +3490,11 @@
       <c r="K68">
         <v>4</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>53</v>
       </c>
@@ -3324,8 +3528,11 @@
       <c r="K69">
         <v>2</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>54</v>
       </c>
@@ -3359,8 +3566,11 @@
       <c r="K70">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>55</v>
       </c>
@@ -3394,8 +3604,11 @@
       <c r="K71">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>56</v>
       </c>
@@ -3429,8 +3642,11 @@
       <c r="K72">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L72">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>57</v>
       </c>
@@ -3464,8 +3680,11 @@
       <c r="K73">
         <v>2</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>58</v>
       </c>
@@ -3499,8 +3718,11 @@
       <c r="K74">
         <v>9</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L74">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>59</v>
       </c>
@@ -3534,8 +3756,11 @@
       <c r="K75">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L75">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>60</v>
       </c>
@@ -3569,8 +3794,11 @@
       <c r="K76">
         <v>2</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>61</v>
       </c>
@@ -3604,8 +3832,11 @@
       <c r="K77">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>62</v>
       </c>
@@ -3639,8 +3870,11 @@
       <c r="K78">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>63</v>
       </c>
@@ -3673,6 +3907,9 @@
       </c>
       <c r="K79">
         <v>2</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3683,14 +3920,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>81</v>
       </c>
@@ -3724,8 +3961,11 @@
       <c r="K1" s="1">
         <v>2025</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -3759,8 +3999,11 @@
       <c r="K2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3794,8 +4037,11 @@
       <c r="K3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -3829,8 +4075,11 @@
       <c r="K4">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3864,8 +4113,11 @@
       <c r="K5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -3899,8 +4151,11 @@
       <c r="K6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -3934,8 +4189,11 @@
       <c r="K7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -3969,8 +4227,11 @@
       <c r="K8">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -4004,8 +4265,11 @@
       <c r="K9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -4039,8 +4303,11 @@
       <c r="K10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -4074,8 +4341,11 @@
       <c r="K11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>64</v>
       </c>
@@ -4109,8 +4379,11 @@
       <c r="K12">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -4144,8 +4417,11 @@
       <c r="K13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -4179,8 +4455,11 @@
       <c r="K14">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -4214,8 +4493,11 @@
       <c r="K15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>65</v>
       </c>
@@ -4249,8 +4531,11 @@
       <c r="K16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -4284,8 +4569,11 @@
       <c r="K17">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>66</v>
       </c>
@@ -4319,8 +4607,11 @@
       <c r="K18">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -4354,8 +4645,11 @@
       <c r="K19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -4389,8 +4683,11 @@
       <c r="K20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -4424,8 +4721,11 @@
       <c r="K21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -4459,8 +4759,11 @@
       <c r="K22">
         <v>6</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -4494,8 +4797,11 @@
       <c r="K23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>67</v>
       </c>
@@ -4529,8 +4835,11 @@
       <c r="K24">
         <v>2</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -4564,8 +4873,11 @@
       <c r="K25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>79</v>
       </c>
@@ -4599,8 +4911,11 @@
       <c r="K26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -4634,8 +4949,11 @@
       <c r="K27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>22</v>
       </c>
@@ -4669,8 +4987,11 @@
       <c r="K28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>23</v>
       </c>
@@ -4704,8 +5025,11 @@
       <c r="K29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -4739,8 +5063,11 @@
       <c r="K30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -4774,8 +5101,11 @@
       <c r="K31">
         <v>11</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -4809,8 +5139,11 @@
       <c r="K32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>26</v>
       </c>
@@ -4844,8 +5177,11 @@
       <c r="K33">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>27</v>
       </c>
@@ -4879,8 +5215,11 @@
       <c r="K34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>28</v>
       </c>
@@ -4914,8 +5253,11 @@
       <c r="K35">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>29</v>
       </c>
@@ -4949,8 +5291,11 @@
       <c r="K36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>30</v>
       </c>
@@ -4984,8 +5329,11 @@
       <c r="K37">
         <v>9</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>31</v>
       </c>
@@ -5019,8 +5367,11 @@
       <c r="K38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>32</v>
       </c>
@@ -5054,8 +5405,11 @@
       <c r="K39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>69</v>
       </c>
@@ -5089,8 +5443,11 @@
       <c r="K40">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>33</v>
       </c>
@@ -5124,8 +5481,11 @@
       <c r="K41">
         <v>2</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>34</v>
       </c>
@@ -5159,8 +5519,11 @@
       <c r="K42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>35</v>
       </c>
@@ -5194,8 +5557,11 @@
       <c r="K43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -5229,8 +5595,11 @@
       <c r="K44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -5264,8 +5633,11 @@
       <c r="K45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>70</v>
       </c>
@@ -5299,8 +5671,11 @@
       <c r="K46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>38</v>
       </c>
@@ -5334,8 +5709,11 @@
       <c r="K47">
         <v>2</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>71</v>
       </c>
@@ -5369,8 +5747,11 @@
       <c r="K48">
         <v>9</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>39</v>
       </c>
@@ -5404,8 +5785,11 @@
       <c r="K49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>40</v>
       </c>
@@ -5439,8 +5823,11 @@
       <c r="K50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>78</v>
       </c>
@@ -5474,8 +5861,11 @@
       <c r="K51">
         <v>9</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>41</v>
       </c>
@@ -5509,8 +5899,11 @@
       <c r="K52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>42</v>
       </c>
@@ -5544,8 +5937,11 @@
       <c r="K53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>43</v>
       </c>
@@ -5579,8 +5975,11 @@
       <c r="K54">
         <v>2</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>44</v>
       </c>
@@ -5614,8 +6013,11 @@
       <c r="K55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>45</v>
       </c>
@@ -5649,8 +6051,11 @@
       <c r="K56">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>46</v>
       </c>
@@ -5684,8 +6089,11 @@
       <c r="K57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>72</v>
       </c>
@@ -5719,8 +6127,11 @@
       <c r="K58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>47</v>
       </c>
@@ -5754,8 +6165,11 @@
       <c r="K59">
         <v>27</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L59">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>48</v>
       </c>
@@ -5789,8 +6203,11 @@
       <c r="K60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>73</v>
       </c>
@@ -5824,8 +6241,11 @@
       <c r="K61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>74</v>
       </c>
@@ -5859,8 +6279,11 @@
       <c r="K62">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>49</v>
       </c>
@@ -5894,8 +6317,11 @@
       <c r="K63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>50</v>
       </c>
@@ -5929,8 +6355,11 @@
       <c r="K64">
         <v>5</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>75</v>
       </c>
@@ -5964,8 +6393,11 @@
       <c r="K65">
         <v>3</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L65">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>51</v>
       </c>
@@ -5999,8 +6431,11 @@
       <c r="K66">
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L66">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>52</v>
       </c>
@@ -6034,8 +6469,11 @@
       <c r="K67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>76</v>
       </c>
@@ -6069,8 +6507,11 @@
       <c r="K68">
         <v>4</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>53</v>
       </c>
@@ -6104,8 +6545,11 @@
       <c r="K69">
         <v>2</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>54</v>
       </c>
@@ -6139,8 +6583,11 @@
       <c r="K70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>55</v>
       </c>
@@ -6174,8 +6621,11 @@
       <c r="K71">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>56</v>
       </c>
@@ -6209,8 +6659,11 @@
       <c r="K72">
         <v>6</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>57</v>
       </c>
@@ -6244,8 +6697,11 @@
       <c r="K73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>58</v>
       </c>
@@ -6279,8 +6735,11 @@
       <c r="K74">
         <v>4</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>59</v>
       </c>
@@ -6314,8 +6773,11 @@
       <c r="K75">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>60</v>
       </c>
@@ -6349,8 +6811,11 @@
       <c r="K76">
         <v>2</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>61</v>
       </c>
@@ -6384,8 +6849,11 @@
       <c r="K77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>62</v>
       </c>
@@ -6419,8 +6887,11 @@
       <c r="K78">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>63</v>
       </c>
@@ -6453,6 +6924,9 @@
       </c>
       <c r="K79">
         <v>2</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6462,13 +6936,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
@@ -6499,8 +6973,11 @@
       <c r="J1" s="1">
         <v>2025</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -6531,8 +7008,11 @@
       <c r="J2">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6563,8 +7043,11 @@
       <c r="J3">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -6595,8 +7078,11 @@
       <c r="J4">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -6627,8 +7113,11 @@
       <c r="J5">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -6659,8 +7148,11 @@
       <c r="J6">
         <v>52</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -6691,8 +7183,11 @@
       <c r="J7">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -6723,8 +7218,11 @@
       <c r="J8">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>78</v>
       </c>
@@ -6755,8 +7253,11 @@
       <c r="J9">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -6787,8 +7288,11 @@
       <c r="J10">
         <v>48</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -6818,6 +7322,9 @@
       </c>
       <c r="J11">
         <v>91</v>
+      </c>
+      <c r="K11">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -6830,13 +7337,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
@@ -6867,8 +7374,11 @@
       <c r="J1" s="1">
         <v>2025</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -6899,8 +7409,11 @@
       <c r="J2">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6931,8 +7444,11 @@
       <c r="J3">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -6963,8 +7479,11 @@
       <c r="J4">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -6995,8 +7514,11 @@
       <c r="J5">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -7027,8 +7549,11 @@
       <c r="J6">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -7059,8 +7584,11 @@
       <c r="J7">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -7091,8 +7619,11 @@
       <c r="J8">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>78</v>
       </c>
@@ -7123,8 +7654,11 @@
       <c r="J9">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -7155,8 +7689,11 @@
       <c r="J10">
         <v>33</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -7186,6 +7723,9 @@
       </c>
       <c r="J11">
         <v>65</v>
+      </c>
+      <c r="K11">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
